--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -19,8 +19,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -131,7 +131,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -172,10 +172,13 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -549,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -641,10 +644,10 @@
           <t>MVP範囲＝一問一答＋自己採点＋要復習。ログイン・サーバーなし</t>
         </is>
       </c>
-      <c r="F2" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G2" s="14" t="n">
+      <c r="F2" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G2" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -684,10 +687,10 @@
           <t>Next.js 16 / TypeScript / Tailwind v4</t>
         </is>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G3" s="14" t="n">
+      <c r="F3" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G3" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -727,10 +730,10 @@
           <t>答えを見る→〇△×の自己採点。キーボード操作（Space / 1・2・3 / Esc）</t>
         </is>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G4" s="14" t="n">
+      <c r="F4" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G4" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -770,10 +773,10 @@
           <t>localStorageに問題ごとの最終評価と回数を保存</t>
         </is>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G5" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -813,10 +816,10 @@
           <t>分野×難易度×出題モード（全部/未回答/要復習/×のみ）×問題数</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G6" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -856,10 +859,10 @@
           <t>歴史36・地理24・政治16・経済14。解説・漢字注意つき</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G7" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -900,25 +903,21 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>リポジトリ作成・push</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G8" s="14" t="n">
+          <t>github.com/tarooooo-u/shakai</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G8" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>課題管理表#1</t>
-        </is>
-      </c>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -942,19 +941,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Vercelで公開</t>
+          <t>Cloudflare Pagesで公開</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>GitHub連携で自動デプロイ。iPadから開けることを確認</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>46299</v>
+          <t>GitHub連携で自動デプロイ（静的書き出し out/）。iPadで確認</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>46300</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -984,23 +983,23 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>roadmap・課題管理表作成</t>
+          <t>問題データのCSV化</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>本ファイル</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="G10" s="14" t="n">
+          <t>content/questions/{history,geography,civics}.csv。ビルド時に検証</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G10" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1008,7 +1007,11 @@
           <t>済</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>旧P1から前倒し</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1022,36 +1025,40 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>P1 使ってもらう</t>
+          <t>P0 Day1 MVP公開</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>息子さんの利用観察</t>
+          <t>単元・テーマで絞り込み</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>46313</v>
+          <t>単元（時代・分野）とタグ（人物・漢字・統計・多答など）</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>ライバル調査より</t>
+        </is>
+      </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1065,38 +1072,38 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>P1 使ってもらう</t>
+          <t>P0 Day1 MVP公開</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>ライバルサイト調査</t>
+          <t>4択モード</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>機能・価格・問題数・UIを比較し差別化ポイントを決める</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>46306</v>
+          <t>CSVの誤答選択肢から出題。正解時は「まぐれ（△）」も選べる</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>URL共有待ち</t>
+          <t>ライバル調査より</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -1112,38 +1119,38 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>P1 使ってもらう</t>
+          <t>P0 Day1 MVP公開</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>問題データの管理方法</t>
+          <t>保護者出題用の一覧</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>スプレッドシート/CSVで管理→questions.tsに変換するスクリプト</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>46306</v>
+          <t>問題と答えの一覧。答えを隠してタップで開く</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>量産の前提</t>
+          <t>ライバル調査より</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1159,36 +1166,40 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>P1 使ってもらう</t>
+          <t>P0 Day1 MVP公開</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>問題300問へ</t>
+          <t>条件をURLで共有</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>46313</v>
+          <t>保護者が範囲を選んでURLを子どもに送る</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>ライバル調査より</t>
+        </is>
+      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1202,33 +1213,33 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>P1 使ってもらう</t>
+          <t>P0 Day1 MVP公開</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>学習記録のバックアップ</t>
+          <t>roadmap・課題管理表作成</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>46313</v>
+          <t>本ファイル</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
@@ -1250,23 +1261,23 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>PWA化</t>
+          <t>息子さんの利用観察</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>ホーム画面に追加してアプリのように起動</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G16" s="14" t="n">
+          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G16" s="16" t="n">
         <v>46313</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1293,28 +1304,28 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>問題の誤り報告</t>
+          <t>ライバルサイト調査</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>46307</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>46313</v>
+          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -1331,29 +1342,29 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>入力式（漢字で書く）モード</t>
+          <t>問題300問へ</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>46314</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>46327</v>
+          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>46313</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1374,7 +1385,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1384,19 +1395,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>学習記録のバックアップ</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>46314</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>46327</v>
+          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>46313</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1417,7 +1428,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1427,19 +1438,19 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>PWA化</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>46328</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>46343</v>
+          <t>ホーム画面に追加してアプリのように起動</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>46313</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1460,7 +1471,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1470,30 +1481,26 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>図表・地図問題</t>
+          <t>問題の誤り報告</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>46328</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>46343</v>
+          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>46313</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>imageUrlは実装済</t>
-        </is>
-      </c>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1517,19 +1524,19 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>入力式（漢字で書く）モード</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>46328</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>46343</v>
+          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>46327</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -1560,19 +1567,19 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>46328</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>46343</v>
+          <t>出来事を古い順に並べる形式</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>46327</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1598,23 +1605,23 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>46314</v>
-      </c>
-      <c r="G24" s="14" t="n">
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>46328</v>
+      </c>
+      <c r="G24" s="16" t="n">
         <v>46343</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1636,36 +1643,40 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>46344</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>46373</v>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>46328</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>46343</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>画像列は実装済</t>
+        </is>
+      </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1679,7 +1690,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1689,26 +1700,30 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>記述対策（自己採点式）</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリスト。AI採点はしない</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>46344</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>46373</v>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>46328</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>46343</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>CSVの地図列は実装済</t>
+        </is>
+      </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1722,7 +1737,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1732,26 +1747,30 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>年表・人物相関図・政治のしくみ図を静止画で表示</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>46344</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>46373</v>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>46327</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1765,7 +1784,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1775,19 +1794,19 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>46344</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>46373</v>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>46328</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>46343</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -1808,25 +1827,29 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="14" t="n">
-        <v>46344</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>46373</v>
+          <t>復習タイミングの自動化</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>46328</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>46343</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -1847,29 +1870,29 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>46374</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>46389</v>
+          <t>統計問題には出典年を持たせる</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>46343</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -1890,29 +1913,29 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>46374</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>46389</v>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>46373</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -1933,29 +1956,29 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>46389</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>46389</v>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>46373</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -1976,36 +1999,36 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="14" t="n">
-        <v>46419</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>46419</v>
+          <t>人物相関図</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>46373</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2019,7 +2042,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2029,19 +2052,19 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>46433</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>46477</v>
+          <t>年表・政治のしくみ図など</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>46373</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -2062,29 +2085,29 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>弱点ダッシュボード</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>46433</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>46477</v>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>46373</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -2105,29 +2128,25 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>46433</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <v>46477</v>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="16" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>46373</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -2148,29 +2167,29 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>46433</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>46477</v>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>46374</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>46389</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -2191,29 +2210,29 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>46477</v>
+          <t>入試直前は新機能より安定を優先</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>46374</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>46389</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2228,70 +2247,414 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="A39" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>P4 仕上げ</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>企画</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>46389</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>46389</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>P4 仕上げ</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>マイルストーン</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="16" t="n">
+        <v>46419</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>46419</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare Workersへ移行</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>46446</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>ログイン・端末間同期</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Supabase等。保護者アカウント＋子ども</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>料金設計・課金</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>利用規約・プライバシーポリシー</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン・集客</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>SEO・塾ママ/パパ向けSNS</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E38">
+  <conditionalFormatting sqref="B2:E46">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I38">
+  <conditionalFormatting sqref="B2:I46">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2408,10 +2771,10 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>gh CLI未インストール。リポジトリ作成とpushにはGitHubアカウントでの認証が必要</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="n">
+          <t>リポジトリ作成とpushにはGitHubアカウントでの認証が必要</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2424,7 +2787,7 @@
           <t>自分</t>
         </is>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -2434,15 +2797,17 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>ローカルのgit初期化・コミットは完了</t>
+          <t>github.com/tarooooo-u/shakai に push 済</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2：着手</t>
-        </is>
-      </c>
-      <c r="K2" s="14" t="n"/>
+          <t>9：完了</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>46299</v>
+      </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="7" t="inlineStr">
@@ -2458,15 +2823,15 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Vercelで公開</t>
+          <t>Cloudflare Pagesで公開</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Vercelアカウントでリポジトリをインポートするだけで公開できる（設定不要）</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="n">
+          <t>Cloudflareでリポジトリを接続。ビルドコマンド npm run build / 出力 out</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2479,24 +2844,28 @@
           <t>自分</t>
         </is>
       </c>
-      <c r="G3" s="14" t="n">
-        <v>46299</v>
+      <c r="G3" s="16" t="n">
+        <v>46300</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1：高</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>静的書き出しの設定は済</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1：未着手</t>
         </is>
       </c>
-      <c r="K3" s="14" t="n"/>
+      <c r="K3" s="16" t="n"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>公開範囲：URLを知っている人のみ。当面は検索除けも検討</t>
+          <t>当面は検索除けも検討</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr"/>
@@ -2513,15 +2882,15 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>問題文の著作権</t>
+          <t>ホスティングの選定</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>将来マネタイズするため、市販教材・塾テキスト・過去問の文章をそのまま使わない</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="n">
+          <t>Vercel無料プランは商用利用不可。将来の課金を考えCloudflareに変更</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2531,28 +2900,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>自分</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>46313</v>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>1：高</t>
+          <t>2：中</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>方針：問題文・解説はすべて自作。questions.tsの先頭にも明記済</t>
+          <t>Cloudflare Pages（今）→ Workers＋OpenNext（ログイン・Stripe導入時）</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2：着手</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="n"/>
+          <t>9：完了</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>46299</v>
+      </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="7" t="inlineStr">
@@ -2568,15 +2939,15 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>問題内容の正確性チェック</t>
+          <t>問題文の著作権</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>初期90問はClaudeが作成。誤りが混ざる可能性がある</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="n">
+          <t>将来マネタイズするため、市販教材・塾テキスト・過去問の文章をそのまま使わない</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2589,26 +2960,26 @@
           <t>自分</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>46306</v>
+      <c r="G5" s="16" t="n">
+        <v>46313</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>1：高</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>方針：問題文・解説はすべて自作。questions.tsの先頭にも明記済</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1：未着手</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>誤り報告ボタンはP1で実装予定</t>
-        </is>
-      </c>
+          <t>2：着手</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr">
         <is>
@@ -2623,15 +2994,15 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>難易度名に学校名を使わない</t>
+          <t>問題内容の正確性チェック</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Gemini案の「開成級」は商用時に避けたい</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
+          <t>初期90問はClaudeが作成。誤りが混ざる可能性がある</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2641,31 +3012,29 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Claude</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>46299</v>
+          <t>自分</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>46306</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>2：中</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>「最難関」に変更</t>
-        </is>
-      </c>
+          <t>1：高</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>9：完了</t>
-        </is>
-      </c>
-      <c r="K6" s="14" t="n">
-        <v>46299</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>1：未着手</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>誤り報告ボタンはP1で実装予定</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="7" t="inlineStr">
         <is>
@@ -2680,15 +3049,15 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>学習記録が端末ごとに別</t>
+          <t>難易度名に学校名を使わない</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>localStorage保存のため、iPadとPCで記録が共有されない。ブラウザのデータ削除で消える</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n">
+          <t>Gemini案の「開成級」は商用時に避けたい</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2701,8 +3070,8 @@
           <t>Claude</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>46313</v>
+      <c r="G7" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -2711,15 +3080,17 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>当面はエクスポート/インポートで対応。本格対応はログイン実装時</t>
+          <t>「最難関」に変更</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1：未着手</t>
-        </is>
-      </c>
-      <c r="K7" s="14" t="n"/>
+          <t>9：完了</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>46299</v>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr">
@@ -2735,15 +3106,15 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>自己採点が甘くなりがち</t>
+          <t>学習記録が端末ごとに別</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>〇を押しがちで定着度が過大評価される</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n">
+          <t>localStorage保存のため、iPadとPCで記録が共有されない。ブラウザのデータ削除で消える</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -2756,8 +3127,8 @@
           <t>Claude</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
-        <v>46327</v>
+      <c r="G8" s="16" t="n">
+        <v>46313</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -2766,7 +3137,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>入力式・選択式モードで補う（P2）</t>
+          <t>当面はエクスポート/インポートで対応。本格対応はログイン実装時</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2774,7 +3145,7 @@
           <t>1：未着手</t>
         </is>
       </c>
-      <c r="K8" s="14" t="n"/>
+      <c r="K8" s="16" t="n"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="7" t="inlineStr">
@@ -2790,15 +3161,15 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>統計データの年次更新</t>
+          <t>自己採点が甘くなりがち</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>生産量ランキング等は毎年変わる</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
+          <t>〇を押しがちで定着度が過大評価される</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -2808,11 +3179,11 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>自分</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>46343</v>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>46327</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -2821,7 +3192,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>入力式・選択式モードで補う（P2）</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2829,7 +3200,7 @@
           <t>1：未着手</t>
         </is>
       </c>
-      <c r="K9" s="14" t="n"/>
+      <c r="K9" s="16" t="n"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="7" t="inlineStr">
@@ -2845,15 +3216,15 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ライバルサイト調査</t>
+          <t>統計データの年次更新</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>比較して差別化ポイントを決める</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
+          <t>生産量ランキング等は毎年変わる</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2866,26 +3237,26 @@
           <t>自分</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>46306</v>
+      <c r="G10" s="16" t="n">
+        <v>46343</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>2：中</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>統計問題には出典年を持たせる</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1：未着手</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>URL共有待ち</t>
-        </is>
-      </c>
+      <c r="K10" s="16" t="n"/>
+      <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr">
         <is>
@@ -2900,15 +3271,15 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>プロジェクトがOneDrive上にある</t>
+          <t>ライバルサイト調査</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>node_modules（数万ファイル）が同期対象になり、重くなったりnpm installが失敗することがある</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
+          <t>比較して差別化ポイントを決める</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>46299</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2918,29 +3289,31 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>自分</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>46313</v>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>46299</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>3：低</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+          <t>2：中</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>単元選択・4択・保護者一覧・URL共有を取り入れ済</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1：未着手</t>
-        </is>
-      </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>OneDrive外へ移すか、同期対象から外す</t>
-        </is>
-      </c>
+          <t>9：完了</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr">
         <is>
@@ -2953,18 +3326,50 @@
         <f>+ROW()-ROW($A$1)</f>
         <v/>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>プロジェクトがOneDrive上にある</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>node_modules（数万ファイル）が同期対象になり、重くなったりnpm installが失敗することがある</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>46299</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>自分</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>3：低</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>1：未着手</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>OneDrive外へ移すか、同期対象から外す</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="7" t="inlineStr">
         <is>
           <t>e</t>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -552,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -1567,12 +1566,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>年号の一問一答</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
+          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
@@ -1586,7 +1585,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>年代並べ替えと同じデータを使える</t>
+        </is>
+      </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1610,19 +1613,19 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+          <t>出来事を古い順に並べる形式</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -1653,12 +1656,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>図表・資料問題</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
@@ -1672,11 +1675,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>画像列は実装済</t>
-        </is>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1700,12 +1699,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>地図で学ぶ地理</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
@@ -1721,7 +1720,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>CSVの地図列は実装済</t>
+          <t>画像列は実装済</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
@@ -1747,19 +1746,19 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>漢字・人物などの軸で参照</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>46327</v>
+        <v>46343</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -1768,7 +1767,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>絞り込みは実装済</t>
+          <t>CSVの地図列は実装済</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
@@ -1794,26 +1793,30 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
         </is>
       </c>
       <c r="F28" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1837,12 +1840,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
         </is>
       </c>
       <c r="F29" s="16" t="n">
@@ -1875,21 +1878,21 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>復習タイミングの自動化</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
         </is>
       </c>
       <c r="F30" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G30" s="16" t="n">
         <v>46343</v>
@@ -1913,7 +1916,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1923,19 +1926,19 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -1961,17 +1964,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F32" s="16" t="n">
@@ -2009,12 +2012,12 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F33" s="16" t="n">
@@ -2052,12 +2055,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>人物相関図</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
         </is>
       </c>
       <c r="F34" s="16" t="n">
@@ -2095,12 +2098,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F35" s="16" t="n">
@@ -2133,15 +2136,19 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+          <t>弱点ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
       <c r="F36" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2167,29 +2174,25 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -2215,17 +2218,17 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
         </is>
       </c>
       <c r="F38" s="16" t="n">
@@ -2258,21 +2261,21 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F39" s="16" t="n">
-        <v>46389</v>
+        <v>46374</v>
       </c>
       <c r="G39" s="16" t="n">
         <v>46389</v>
@@ -2301,31 +2304,31 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
       <c r="F40" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I40" s="3" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2339,36 +2342,36 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>46446</v>
+        <v>46419</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2392,19 +2395,19 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F42" s="16" t="n">
         <v>46433</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -2430,17 +2433,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase等。保護者アカウント＋子ども</t>
         </is>
       </c>
       <c r="F43" s="16" t="n">
@@ -2478,12 +2481,12 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F44" s="16" t="n">
@@ -2521,12 +2524,12 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F45" s="16" t="n">
@@ -2559,21 +2562,21 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G46" s="16" t="n">
         <v>46477</v>
@@ -2591,70 +2594,113 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="A47" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E46">
+  <conditionalFormatting sqref="B2:E47">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I46">
+  <conditionalFormatting sqref="B2:I47">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -1360,17 +1360,21 @@
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>46313</v>
+        <v>46299</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>白地図問題374問を追加し計464問</t>
+        </is>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1389,24 +1393,24 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>学習記録のバックアップ</t>
+          <t>白地図問題の地図座標</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
+          <t>地図機能に向けてCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
         </is>
       </c>
       <c r="F19" s="16" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1437,12 +1441,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>PWA化</t>
+          <t>学習記録のバックアップ</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>ホーム画面に追加してアプリのように起動</t>
+          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
@@ -1480,12 +1484,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>問題の誤り報告</t>
+          <t>PWA化</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
+          <t>ホーム画面に追加してアプリのように起動</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
@@ -1513,7 +1517,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1523,19 +1527,19 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>入力式（漢字で書く）モード</t>
+          <t>問題の誤り報告</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
+          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -1566,12 +1570,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>年号の一問一答</t>
+          <t>入力式（漢字で書く）モード</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
+          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
@@ -1585,11 +1589,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>年代並べ替えと同じデータを使える</t>
-        </is>
-      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>年号の一問一答</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
+          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
@@ -1632,7 +1632,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>年代並べ替えと同じデータを使える</t>
+        </is>
+      </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1656,19 +1660,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+          <t>出来事を古い順に並べる形式</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -1699,12 +1703,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>図表・資料問題</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
@@ -1718,11 +1722,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>画像列は実装済</t>
-        </is>
-      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>地図で学ぶ地理</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>CSVの地図列は実装済</t>
+          <t>画像列は実装済</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>漢字・人物などの軸で参照</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
         </is>
       </c>
       <c r="F28" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>46327</v>
+        <v>46343</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>絞り込みは実装済</t>
+          <t>CSVの地図列は実装済</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -1840,26 +1840,30 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
         </is>
       </c>
       <c r="F29" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1883,12 +1887,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
         </is>
       </c>
       <c r="F30" s="16" t="n">
@@ -1921,21 +1925,21 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>復習タイミングの自動化</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G31" s="16" t="n">
         <v>46343</v>
@@ -1959,7 +1963,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1969,19 +1973,19 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F32" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -2007,17 +2011,17 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F33" s="16" t="n">
@@ -2055,12 +2059,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F34" s="16" t="n">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>人物相関図</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
         </is>
       </c>
       <c r="F35" s="16" t="n">
@@ -2141,12 +2145,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F36" s="16" t="n">
@@ -2179,15 +2183,19 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
+          <t>弱点ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
       <c r="F37" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2213,29 +2221,25 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr"/>
       <c r="F38" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2261,17 +2265,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
         </is>
       </c>
       <c r="F39" s="16" t="n">
@@ -2304,21 +2308,21 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F40" s="16" t="n">
-        <v>46389</v>
+        <v>46374</v>
       </c>
       <c r="G40" s="16" t="n">
         <v>46389</v>
@@ -2347,31 +2351,31 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
       <c r="F41" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2385,36 +2389,36 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>46446</v>
+        <v>46419</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2438,19 +2442,19 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F43" s="16" t="n">
         <v>46433</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -2476,17 +2480,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase等。保護者アカウント＋子ども</t>
         </is>
       </c>
       <c r="F44" s="16" t="n">
@@ -2524,12 +2528,12 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F45" s="16" t="n">
@@ -2567,12 +2571,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
@@ -2605,21 +2609,21 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F47" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>46477</v>
@@ -2637,70 +2641,113 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="A48" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E47">
+  <conditionalFormatting sqref="B2:E48">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I47">
+  <conditionalFormatting sqref="B2:I48">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>息子さんの利用観察</t>
+          <t>e-Stat APIで統計データ取得</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
+          <t>水揚げ量・農産物の生産量・工業出荷額などを取得し、出典・年つきで保存。統計問題の要確認を解消</t>
         </is>
       </c>
       <c r="F16" s="16" t="n">
@@ -1284,7 +1284,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>アプリID取得済み（2026/10/4）</t>
+        </is>
+      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1303,28 +1307,28 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ライバルサイト調査</t>
+          <t>息子さんの利用観察</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
+          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
         </is>
       </c>
       <c r="F17" s="16" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>済</t>
+          <t>未</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -1346,17 +1350,17 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>問題300問へ</t>
+          <t>ライバルサイト調査</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
+          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
         </is>
       </c>
       <c r="F18" s="16" t="n">
@@ -1370,11 +1374,7 @@
           <t>済</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>白地図問題374問を追加し計464問</t>
-        </is>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1398,26 +1398,30 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>白地図問題の地図座標</t>
+          <t>問題300問へ</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>地図機能に向けてCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
+          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
         </is>
       </c>
       <c r="F19" s="16" t="n">
-        <v>46314</v>
+        <v>46299</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>46327</v>
+        <v>46299</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>白地図問題374問を追加し計464問</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1436,24 +1440,24 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>学習記録のバックアップ</t>
+          <t>白地図問題の地図座標</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
+          <t>地図機能に向けてCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1484,12 +1488,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>PWA化</t>
+          <t>学習記録のバックアップ</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ホーム画面に追加してアプリのように起動</t>
+          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
@@ -1527,12 +1531,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>問題の誤り報告</t>
+          <t>PWA化</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
+          <t>ホーム画面に追加してアプリのように起動</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
@@ -1560,7 +1564,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1570,19 +1574,19 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>入力式（漢字で書く）モード</t>
+          <t>問題の誤り報告</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
+          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1613,12 +1617,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>年号の一問一答</t>
+          <t>入力式（漢字で書く）モード</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
+          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
@@ -1632,11 +1636,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>年代並べ替えと同じデータを使える</t>
-        </is>
-      </c>
+      <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>年号の一問一答</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
+          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
@@ -1679,7 +1679,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>年代並べ替えと同じデータを使える</t>
+        </is>
+      </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1703,19 +1707,19 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+          <t>出来事を古い順に並べる形式</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -1746,12 +1750,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>図表・資料問題</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
@@ -1765,11 +1769,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>画像列は実装済</t>
-        </is>
-      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>地図で学ぶ地理</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
         </is>
       </c>
       <c r="F28" s="16" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>CSVの地図列は実装済</t>
+          <t>画像列は実装済</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -1840,19 +1840,19 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>漢字・人物などの軸で参照</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
         </is>
       </c>
       <c r="F29" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>46327</v>
+        <v>46343</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>絞り込みは実装済</t>
+          <t>CSVの地図列は実装済</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -1887,26 +1887,30 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
         </is>
       </c>
       <c r="F30" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1930,12 +1934,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
         </is>
       </c>
       <c r="F31" s="16" t="n">
@@ -1968,21 +1972,21 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>復習タイミングの自動化</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
         </is>
       </c>
       <c r="F32" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G32" s="16" t="n">
         <v>46343</v>
@@ -2006,7 +2010,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2016,19 +2020,19 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F33" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -2054,17 +2058,17 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F34" s="16" t="n">
@@ -2102,12 +2106,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F35" s="16" t="n">
@@ -2145,12 +2149,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>人物相関図</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
         </is>
       </c>
       <c r="F36" s="16" t="n">
@@ -2188,12 +2192,12 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F37" s="16" t="n">
@@ -2226,15 +2230,19 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
+          <t>弱点ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
       <c r="F38" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2260,29 +2268,25 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2308,17 +2312,17 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
         </is>
       </c>
       <c r="F40" s="16" t="n">
@@ -2351,21 +2355,21 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F41" s="16" t="n">
-        <v>46389</v>
+        <v>46374</v>
       </c>
       <c r="G41" s="16" t="n">
         <v>46389</v>
@@ -2394,31 +2398,31 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
       <c r="F42" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2432,36 +2436,36 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>46446</v>
+        <v>46419</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2485,19 +2489,19 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F44" s="16" t="n">
         <v>46433</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -2523,17 +2527,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase等。保護者アカウント＋子ども</t>
         </is>
       </c>
       <c r="F45" s="16" t="n">
@@ -2571,12 +2575,12 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
@@ -2614,12 +2618,12 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F47" s="16" t="n">
@@ -2652,21 +2656,21 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F48" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G48" s="16" t="n">
         <v>46477</v>
@@ -2684,70 +2688,160 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J49" s="15" t="inlineStr">
+      <c r="A49" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン移行時のAPI設定</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>e-Statはマイページで名称・URLを後から変更できる</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J51" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E48">
+  <conditionalFormatting sqref="B2:E50">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I48">
+  <conditionalFormatting sqref="B2:I50">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -1270,23 +1270,23 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>水揚げ量・農産物の生産量・工業出荷額などを取得し、出典・年つきで保存。統計問題の要確認を解消</t>
+          <t>果物・茶の生産量、漁港別出荷量を取得（npm run stats）。統計問題13問に出典・年を記入</t>
         </is>
       </c>
       <c r="F16" s="16" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>46313</v>
+        <v>46299</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>アプリID取得済み（2026/10/4）</t>
+          <t>2024年産データ</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>息子さんの利用観察</t>
+          <t>統計データの追加取得</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
+          <t>工業出荷額（工業地帯）・都道府県人口・米・野菜など。残りの要確認を解消</t>
         </is>
       </c>
       <c r="F17" s="16" t="n">
@@ -1331,7 +1331,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>漁港は「上場水揚量」の表がAPIにないため主要品目の出荷量で代用中</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1350,28 +1354,28 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ライバルサイト調査</t>
+          <t>息子さんの利用観察</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
+          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>済</t>
+          <t>未</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
@@ -1393,17 +1397,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>問題300問へ</t>
+          <t>ライバルサイト調査</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
+          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
         </is>
       </c>
       <c r="F19" s="16" t="n">
@@ -1417,11 +1421,7 @@
           <t>済</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>白地図問題374問を追加し計464問</t>
-        </is>
-      </c>
+      <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1445,26 +1445,30 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>白地図問題の地図座標</t>
+          <t>問題300問へ</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>地図機能に向けてCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
+          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>46314</v>
+        <v>46299</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>46327</v>
+        <v>46299</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>白地図問題374問を追加し計464問</t>
+        </is>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1483,24 +1487,24 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>学習記録のバックアップ</t>
+          <t>白地図問題の地図座標</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
+          <t>地図機能に向けてCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -1531,12 +1535,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>PWA化</t>
+          <t>学習記録のバックアップ</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>ホーム画面に追加してアプリのように起動</t>
+          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
@@ -1574,12 +1578,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>問題の誤り報告</t>
+          <t>PWA化</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
+          <t>ホーム画面に追加してアプリのように起動</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
@@ -1607,7 +1611,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1617,19 +1621,19 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>入力式（漢字で書く）モード</t>
+          <t>問題の誤り報告</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
+          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -1660,12 +1664,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>年号の一問一答</t>
+          <t>入力式（漢字で書く）モード</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
+          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
@@ -1679,11 +1683,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>年代並べ替えと同じデータを使える</t>
-        </is>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>年号の一問一答</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
+          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
@@ -1726,7 +1726,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>年代並べ替えと同じデータを使える</t>
+        </is>
+      </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1750,19 +1754,19 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+          <t>出来事を古い順に並べる形式</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -1793,12 +1797,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>図表・資料問題</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
         </is>
       </c>
       <c r="F28" s="16" t="n">
@@ -1812,11 +1816,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>画像列は実装済</t>
-        </is>
-      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>地図で学ぶ地理</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
         </is>
       </c>
       <c r="F29" s="16" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>CSVの地図列は実装済</t>
+          <t>画像列は実装済</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -1887,19 +1887,19 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>漢字・人物などの軸で参照</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
         </is>
       </c>
       <c r="F30" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>46327</v>
+        <v>46343</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>絞り込みは実装済</t>
+          <t>CSVの地図列は実装済</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -1934,26 +1934,30 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1977,12 +1981,12 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
         </is>
       </c>
       <c r="F32" s="16" t="n">
@@ -2015,21 +2019,21 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>復習タイミングの自動化</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
         </is>
       </c>
       <c r="F33" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G33" s="16" t="n">
         <v>46343</v>
@@ -2053,7 +2057,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2063,19 +2067,19 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F34" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -2101,17 +2105,17 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F35" s="16" t="n">
@@ -2149,12 +2153,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F36" s="16" t="n">
@@ -2192,12 +2196,12 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>人物相関図</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
         </is>
       </c>
       <c r="F37" s="16" t="n">
@@ -2235,12 +2239,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F38" s="16" t="n">
@@ -2273,15 +2277,19 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
+          <t>弱点ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
       <c r="F39" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2307,29 +2315,25 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
@@ -2355,17 +2359,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
         </is>
       </c>
       <c r="F41" s="16" t="n">
@@ -2398,21 +2402,21 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F42" s="16" t="n">
-        <v>46389</v>
+        <v>46374</v>
       </c>
       <c r="G42" s="16" t="n">
         <v>46389</v>
@@ -2441,31 +2445,31 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
       <c r="F43" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2479,36 +2483,36 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>46446</v>
+        <v>46419</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2532,19 +2536,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F45" s="16" t="n">
         <v>46433</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2570,17 +2574,17 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase等。保護者アカウント＋子ども</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
@@ -2618,12 +2622,12 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F47" s="16" t="n">
@@ -2661,12 +2665,12 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F48" s="16" t="n">
@@ -2699,17 +2703,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン移行時のAPI設定</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F49" s="16" t="n">
@@ -2723,11 +2727,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>e-Statはマイページで名称・URLを後から変更できる</t>
-        </is>
-      </c>
+      <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2746,21 +2746,21 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン移行時のAPI設定</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
         </is>
       </c>
       <c r="F50" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G50" s="16" t="n">
         <v>46477</v>
@@ -2770,7 +2770,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>e-Statはマイページで名称・URLを後から変更できる</t>
+        </is>
+      </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2778,70 +2782,113 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J51" s="15" t="inlineStr">
+      <c r="A51" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E50">
+  <conditionalFormatting sqref="B2:E51">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I50">
+  <conditionalFormatting sqref="B2:I51">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -1354,31 +1354,35 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>息子さんの利用観察</t>
+          <t>サイドバー（開閉式）</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
+          <t>お気に入り／歴史・地理・公民／漢字間違えやすい／間違えた問題 などへすぐ移動できるメニュー。お気に入り（★）機能もあわせて作る。まずUIイメージを確認してから実装</t>
         </is>
       </c>
       <c r="F18" s="16" t="n">
         <v>46300</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>優先度：高</t>
+        </is>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1397,17 +1401,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>ライバルサイト調査</t>
+          <t>雨温図問題（気象庁の平年値）</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
+          <t>26都市×2問（どの都市か／どの気候区分か）。雨温図はアプリ内でグラフを描画（npm run climate）</t>
         </is>
       </c>
       <c r="F19" s="16" t="n">
@@ -1421,7 +1425,11 @@
           <t>済</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2020年平年値</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1440,35 +1448,31 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>問題300問へ</t>
+          <t>息子さんの利用観察</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
+          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>済</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>白地図問題374問を追加し計464問</t>
-        </is>
-      </c>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1487,28 +1491,28 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>白地図問題の地図座標</t>
+          <t>ライバルサイト調査</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>地図機能に向けてCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
+          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>46314</v>
+        <v>46299</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>46327</v>
+        <v>46299</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1530,31 +1534,35 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>学習記録のバックアップ</t>
+          <t>問題300問へ</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
+          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
-        <v>46307</v>
+        <v>46299</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>46313</v>
+        <v>46299</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>白地図問題374問を追加し計464問</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1573,24 +1581,24 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>PWA化</t>
+          <t>白地図問題の地図座標</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ホーム画面に追加してアプリのように起動</t>
+          <t>国土地理院の地名検索APIでCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1621,12 +1629,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>問題の誤り報告</t>
+          <t>学習記録のバックアップ</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
+          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
@@ -1654,7 +1662,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1664,19 +1672,19 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>入力式（漢字で書く）モード</t>
+          <t>PWA化</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
+          <t>ホーム画面に追加してアプリのように起動</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -1697,7 +1705,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1707,30 +1715,26 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>年号の一問一答</t>
+          <t>問題の誤り報告</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
+          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>年代並べ替えと同じデータを使える</t>
-        </is>
-      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1754,12 +1758,12 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>入力式（漢字で書く）モード</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
+          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
@@ -1797,26 +1801,30 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>年号の一問一答</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
         </is>
       </c>
       <c r="F28" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>年代並べ替えと同じデータを使える</t>
+        </is>
+      </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1840,30 +1848,26 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>図表・資料問題</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+          <t>出来事を古い順に並べる形式</t>
         </is>
       </c>
       <c r="F29" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>画像列は実装済</t>
-        </is>
-      </c>
+      <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1887,12 +1891,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>地図で学ぶ地理</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
         </is>
       </c>
       <c r="F30" s="16" t="n">
@@ -1906,11 +1910,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>CSVの地図列は実装済</t>
-        </is>
-      </c>
+      <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1934,19 +1934,19 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>漢字・人物などの軸で参照</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>46327</v>
+        <v>46343</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>絞り込みは実装済</t>
+          <t>画像列は実装済</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
         </is>
       </c>
       <c r="F32" s="16" t="n">
@@ -2000,7 +2000,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>CSVの地図列は実装済</t>
+        </is>
+      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2024,26 +2028,30 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
         </is>
       </c>
       <c r="F33" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2062,21 +2070,21 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
         </is>
       </c>
       <c r="F34" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G34" s="16" t="n">
         <v>46343</v>
@@ -2100,29 +2108,29 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>復習タイミングの自動化</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
         </is>
       </c>
       <c r="F35" s="16" t="n">
-        <v>46344</v>
+        <v>46328</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -2143,36 +2151,40 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>世界の生産量ランキング</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>FAOSTAT（国連食糧農業機関）のデータで、小麦・米・とうもろこし・大豆などの生産国ランキング問題を作る</t>
         </is>
       </c>
       <c r="F36" s="16" t="n">
-        <v>46344</v>
+        <v>46328</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>一括ダウンロードは登録不要</t>
+        </is>
+      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2186,29 +2198,29 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F37" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -2234,17 +2246,17 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F38" s="16" t="n">
@@ -2282,12 +2294,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F39" s="16" t="n">
@@ -2320,15 +2332,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
+          <t>人物相関図</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+        </is>
+      </c>
       <c r="F40" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2354,7 +2370,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2364,19 +2380,19 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F41" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -2397,29 +2413,29 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>弱点ダッシュボード</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>分野・時代・単元ごとの正答率</t>
         </is>
       </c>
       <c r="F42" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -2440,29 +2456,25 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Day90</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="16" t="n">
-        <v>46389</v>
+        <v>46344</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -2488,31 +2500,31 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>総復習モード</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
+        </is>
+      </c>
       <c r="F44" s="16" t="n">
-        <v>46419</v>
+        <v>46374</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2526,29 +2538,29 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F45" s="16" t="n">
-        <v>46433</v>
+        <v>46374</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>46446</v>
+        <v>46389</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2569,29 +2581,29 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>90日MVP完了</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
+          <t>Day90</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
-        <v>46433</v>
+        <v>46389</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>46477</v>
+        <v>46389</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
@@ -2612,36 +2624,36 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G47" s="16" t="n">
-        <v>46477</v>
+        <v>46419</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2660,24 +2672,24 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F48" s="16" t="n">
         <v>46433</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>46477</v>
+        <v>46446</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
@@ -2703,17 +2715,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>Supabase等。保護者アカウント＋子ども</t>
         </is>
       </c>
       <c r="F49" s="16" t="n">
@@ -2746,17 +2758,17 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン移行時のAPI設定</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F50" s="16" t="n">
@@ -2770,11 +2782,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>e-Statはマイページで名称・URLを後から変更できる</t>
-        </is>
-      </c>
+      <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2793,21 +2801,21 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F51" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G51" s="16" t="n">
         <v>46477</v>
@@ -2825,70 +2833,246 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J52" s="15" t="inlineStr">
+      <c r="A52" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン・集客</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>SEO・塾ママ/パパ向けSNS</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン移行時のAPI設定</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>46433</v>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>e-Statはマイページで名称・URLを後から変更できる</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>P6 いつか</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>白地図に描いて覚える</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>国土数値情報（川・湖・海岸線の形）で白地図を描き、川をなぞる・場所をタップするなどで答える</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="16" t="n"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>自己満足に近いかも。余裕があれば</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J56" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E51">
+  <conditionalFormatting sqref="B2:E55">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I51">
+  <conditionalFormatting sqref="B2:I55">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -1364,18 +1364,18 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>お気に入り／歴史・地理・公民／漢字間違えやすい／間違えた問題 などへすぐ移動できるメニュー。お気に入り（★）機能もあわせて作る。まずUIイメージを確認してから実装</t>
+          <t>お気に入り／間違えた問題／歴史・地理・公民／テーマ（漢字・白地図・雨温図・人物）／問題と答えの一覧。PCは縮められる、スマホは重ねて開く。★お気に入り（Fキーでも）</t>
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -9,7 +9,9 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="roadmap" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="課題管理表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="リスト" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="サーバー設計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="費用見積" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="リスト" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Meiryo UI"/>
       <charset val="128"/>
@@ -79,6 +82,11 @@
       <color theme="0" tint="-0.249977111117893"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -130,7 +138,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -176,6 +184,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -238,6 +252,21 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>決めた内容をここに記入（DBスペシャリストの判断）</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -2715,31 +2744,35 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>サーバー設計の決定</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Supabase等。保護者アカウント＋子ども</t>
+          <t>アカウントのモデル・学習記録の持ち方・RLS・課金の表など（シート「サーバー設計」）。Claudeが DDL と RLS の叩き台を作り、決定は本人</t>
         </is>
       </c>
       <c r="F49" s="16" t="n">
-        <v>46433</v>
+        <v>46420</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>46477</v>
+        <v>46432</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>DBスペシャリストとして判断</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2758,17 +2791,17 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase（PostgreSQL＋認証＋RLS）を第一候補。保護者アカウント＋子どもプロフィール。費用はシート「費用見積」</t>
         </is>
       </c>
       <c r="F50" s="16" t="n">
@@ -2806,12 +2839,12 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F51" s="16" t="n">
@@ -2849,12 +2882,12 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F52" s="16" t="n">
@@ -2887,17 +2920,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン移行時のAPI設定</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F53" s="16" t="n">
@@ -2911,11 +2944,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>e-Statはマイページで名称・URLを後から変更できる</t>
-        </is>
-      </c>
+      <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2934,21 +2963,21 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン移行時のAPI設定</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
         </is>
       </c>
       <c r="F54" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G54" s="16" t="n">
         <v>46477</v>
@@ -2958,7 +2987,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>e-Statはマイページで名称・URLを後から変更できる</t>
+        </is>
+      </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2972,107 +3005,150 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t>P6 いつか</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>開発</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>白地図に描いて覚える</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>国土数値情報（川・湖・海岸線の形）で白地図を描き、川をなぞる・場所をタップするなどで答える</t>
         </is>
       </c>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>自己満足に近いかも。余裕があれば</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I56" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J56" s="15" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J57" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E55">
+  <conditionalFormatting sqref="B2:E56">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I55">
+  <conditionalFormatting sqref="B2:I56">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4334,6 +4410,695 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" style="13" min="1" max="1"/>
+    <col width="20" customWidth="1" style="13" min="2" max="2"/>
+    <col width="30" customWidth="1" style="13" min="3" max="3"/>
+    <col width="50" customWidth="1" style="13" min="4" max="4"/>
+    <col width="44" customWidth="1" style="13" min="5" max="5"/>
+    <col width="18" customWidth="1" style="13" min="6" max="6"/>
+    <col width="36" customWidth="1" style="13" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>論点</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>決めること</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Claudeの推奨</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>決定</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>アカウントのモデル</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>誰がログインし、誰の記録を持つか</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>A: 保護者だけログイン、子どもは保護者の下のプロフィール（メール不要）
+B: 子どもも個別にログイン</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>A（子どもの個人情報を持たない。課金主体＝保護者）</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>子ども向けサービスなので保護者の同意を前提に</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>学習記録の持ち方</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>解答の記録を、追記型にするか最新状態だけにするか</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>A: 解答イベント表（追記のみ）＋問題ごとの最新状態
+B: 最新状態だけ</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>A（オフラインで解いた分も後から和集合で取り込めて矛盾しない。最新状態はイベントから再計算できる）</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>イベントにはクライアント生成のIDを持たせて二重登録を防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>問題データの置き場所</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>問題本体をDBに入れるか</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>A: 問題はCSV（Git管理）のまま、DBは問題IDだけ
+B: 問題表をDBにも作り外部キーを張る</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>A（作問の流れを変えない）。Bにする場合はビルド時に問題表へ同期</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>問題IDは変更禁止（今のルールのまま）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>アクセス制御（RLS）</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>どの単位で行を見せるか</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>家族（family_id）単位で、保護者はその家族の全プロフィールを読める</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>family_id 単位のRLS</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>管理者用の操作はサーバー側のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>課金まわりの表</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Stripeとの対応づけ</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>契約（subscriptions）・利用できる権利（entitlements）・Stripe顧客ID・処理済みwebhook（二重処理防止）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>webhookはイベントIDで冪等に処理</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>有料の問題はログイン後にサーバーから配る（静的ファイルに含めない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>オフライン対応</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>電波のないところで解いた記録の扱い</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ブラウザ保存をキャッシュとして残し、送信待ちキューから順に送る</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>解答イベントの追記なら競合しない</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>今ある記録の移行</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>サーバー導入前にブラウザに貯まった記録</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>初回ログイン時に localStorage の学習記録・お気に入りをアップロード</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>初回ログイン時に一度だけ取り込む</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <f>ROW()-1</f>
+        <v/>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>データの削除・書き出し</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>退会時と本人からの請求</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>アカウント削除で家族単位で削除。CSV/JSONで書き出し</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>個人情報保護法への対応。利用規約・プライバシーポリシーに明記</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="13" min="1" max="1"/>
+    <col width="40" customWidth="1" style="13" min="2" max="2"/>
+    <col width="10" customWidth="1" style="13" min="3" max="3"/>
+    <col width="12" customWidth="1" style="13" min="4" max="4"/>
+    <col width="12" customWidth="1" style="13" min="5" max="5"/>
+    <col width="56" customWidth="1" style="13" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>月額（円）</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>年額（円）</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>前提</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>為替（1ドルあたりの円）</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>料金はドル建て。契約前に最新の料金を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>今（息子だけ・サーバーなし）</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare Pages・GitHub・e-Stat・気象庁</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="18">
+        <f>D3*12</f>
+        <v/>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>すべて無料枠</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>サーバーあり（家族・小規模公開）</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Supabase 無料プラン</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18">
+        <f>D4*12</f>
+        <v/>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>DB 500MBまで。7日間アクセスがないと休止。自動バックアップなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>サーバーあり（家族・小規模公開）</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン（年額を12で割って月額に）</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18">
+        <f>E5/12</f>
+        <v/>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare Registrar は原価販売。.com でおよそ年1,500〜2,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（最小構成）</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Supabase 無料プラン</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18">
+        <f>D6*12</f>
+        <v/>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>利用者がいれば休止しない。バックアップは自前（pg_dump を定期実行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（最小構成）</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18">
+        <f>E7/12</f>
+        <v/>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（最小構成）</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="18">
+        <f>D8*12</f>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>月額なし。決済ごとに約3.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（本格）</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Supabase Pro（25ドル）</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18">
+        <f>25*$C$2</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>D9*12</f>
+        <v/>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>自動バックアップ・休止なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（本格）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare Workers 有料（5ドル）</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18">
+        <f>5*$C$2</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>D10*12</f>
+        <v/>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>サーバー処理が無料枠を超えたら</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（本格）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>独自ドメイン</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18">
+        <f>E11/12</f>
+        <v/>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>段階ごとの月額合計（決済手数料を除く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>今（息子だけ・サーバーなし）</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="18">
+        <f>SUMIF($A$3:$A$11,A14,$D$3:$D$11)</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>D14*12</f>
+        <v/>
+      </c>
+      <c r="F14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>サーバーあり（家族・小規模公開）</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="18">
+        <f>SUMIF($A$3:$A$11,A15,$D$3:$D$11)</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>D15*12</f>
+        <v/>
+      </c>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（最小構成）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="18">
+        <f>SUMIF($A$3:$A$11,A16,$D$3:$D$11)</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f>D16*12</f>
+        <v/>
+      </c>
+      <c r="F16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>有料公開（本格）</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="18">
+        <f>SUMIF($A$3:$A$11,A17,$D$3:$D$11)</f>
+        <v/>
+      </c>
+      <c r="E17" s="18">
+        <f>D17*12</f>
+        <v/>
+      </c>
+      <c r="F17" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>青字＝入力値（料金・為替）、黒字＝数式。料金は2026年10月時点の目安</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -1346,23 +1346,23 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>工業出荷額（工業地帯）・都道府県人口・米・野菜など。残りの要確認を解消</t>
+          <t>米・野菜16品目・畜産5種・都道府県人口を追加し、全国1位の統計問題26問</t>
         </is>
       </c>
       <c r="F17" s="16" t="n">
         <v>46300</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>46313</v>
+        <v>46300</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>済</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>漁港は「上場水揚量」の表がAPIにないため主要品目の出荷量で代用中</t>
+          <t>工業出荷額は最新の表がAPIにないため未対応（要確認のまま）</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1388,19 +1388,19 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>サイドバー（開閉式）</t>
+          <t>写真・絵で答える問題</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>お気に入り／間違えた問題／歴史・地理・公民／テーマ（漢字・白地図・雨温図・人物）／問題と答えの一覧。PCは縮められる、スマホは重ねて開く。★お気に入り（Fキーでも）</t>
+          <t>Wikimedia Commons の画像34点（建築・美術・人物）で、写真→名前／名前→写真4択の68問。出典ページを自動生成</t>
         </is>
       </c>
       <c r="F18" s="16" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>優先度：高</t>
+          <t>画像は今後も追加（npm run images）</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -1430,17 +1430,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>雨温図問題（気象庁の平年値）</t>
+          <t>サイドバー（開閉式）</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>26都市×2問（どの都市か／どの気候区分か）。雨温図はアプリ内でグラフを描画（npm run climate）</t>
+          <t>お気に入り／間違えた問題／歴史・地理・公民／テーマ（漢字・白地図・雨温図・人物）／問題と答えの一覧。PCは縮められる、スマホは重ねて開く。★お気に入り（Fキーでも）</t>
         </is>
       </c>
       <c r="F19" s="16" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2020年平年値</t>
+          <t>優先度：高</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1477,31 +1477,35 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>検証</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>息子さんの利用観察</t>
+          <t>雨温図問題（気象庁の平年値）</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
+          <t>26都市×2問（どの都市か／どの気候区分か）。雨温図はアプリ内でグラフを描画（npm run climate）</t>
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>46313</v>
+        <v>46299</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>2020年平年値</t>
+        </is>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1520,28 +1524,28 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>検証</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>ライバルサイト調査</t>
+          <t>息子さんの利用観察</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
+          <t>1日5〜10分。テンポ・操作の不満をメモ→課題管理表へ</t>
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>済</t>
+          <t>未</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1563,17 +1567,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>問題300問へ</t>
+          <t>ライバルサイト調査</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
+          <t>5サイトの機能を列挙。差別化＝間違えた問題の記録と復習</t>
         </is>
       </c>
       <c r="F22" s="16" t="n">
@@ -1587,11 +1591,7 @@
           <t>済</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>白地図問題374問を追加し計464問</t>
-        </is>
-      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1615,26 +1615,30 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>白地図問題の地図座標</t>
+          <t>問題300問へ</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>国土地理院の地名検索APIでCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
+          <t>塾の単元進度・苦手分野から優先。文章は自作</t>
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>46314</v>
+        <v>46299</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>46327</v>
+        <v>46299</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>未</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>白地図問題374問を追加し計464問</t>
+        </is>
+      </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1653,24 +1657,24 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>学習記録のバックアップ</t>
+          <t>白地図問題の地図座標</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
+          <t>国土地理院の地名検索APIでCSVの地図列（緯度,経度）を埋める。地点ごとに確認しながら</t>
         </is>
       </c>
       <c r="F24" s="16" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -1701,12 +1705,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>PWA化</t>
+          <t>学習記録のバックアップ</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>ホーム画面に追加してアプリのように起動</t>
+          <t>JSONエクスポート/インポート（端末変更・ブラウザ削除対策）</t>
         </is>
       </c>
       <c r="F25" s="16" t="n">
@@ -1744,12 +1748,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>問題の誤り報告</t>
+          <t>PWA化</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
+          <t>ホーム画面に追加してアプリのように起動</t>
         </is>
       </c>
       <c r="F26" s="16" t="n">
@@ -1777,7 +1781,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>P2 最難関対策の強化</t>
+          <t>P1 使ってもらう</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1787,19 +1791,19 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>入力式（漢字で書く）モード</t>
+          <t>問題の誤り報告</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
+          <t>問題ごとに「おかしい？」ボタン→メモ保存</t>
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -1830,12 +1834,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>年号の一問一答</t>
+          <t>入力式（漢字で書く）モード</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
+          <t>自己採点の甘さ対策。表記ゆれは別解リストで判定</t>
         </is>
       </c>
       <c r="F28" s="16" t="n">
@@ -1849,11 +1853,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>年代並べ替えと同じデータを使える</t>
-        </is>
-      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1877,12 +1877,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>年代並べ替え問題</t>
+          <t>年号の一問一答</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>出来事を古い順に並べる形式</t>
+          <t>「出来事→何年？」「○年→何が起きた？」の両方向。年表CSV（年・出来事・単元）から自動で問題を作る案</t>
         </is>
       </c>
       <c r="F29" s="16" t="n">
@@ -1896,7 +1896,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>年代並べ替えと同じデータを使える</t>
+        </is>
+      </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -1920,19 +1924,19 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>正誤判定問題</t>
+          <t>年代並べ替え問題</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
+          <t>出来事を古い順に並べる形式</t>
         </is>
       </c>
       <c r="F30" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -1963,12 +1967,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>図表・資料問題</t>
+          <t>正誤判定問題</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
+          <t>「誤っているものを選べ」形式。条件読み飛ばし対策</t>
         </is>
       </c>
       <c r="F31" s="16" t="n">
@@ -1982,11 +1986,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>画像列は実装済</t>
-        </is>
-      </c>
+      <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>地図で学ぶ地理</t>
+          <t>図表・資料問題</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
+          <t>雨温図・地形図・統計グラフ・史料の画像を問題に表示</t>
         </is>
       </c>
       <c r="F32" s="16" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>CSVの地図列は実装済</t>
+          <t>画像列は実装済</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>漢字・人物などの軸で参照</t>
+          <t>地図で学ぶ地理</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
+          <t>地図上のピンで場所を答える・問題の場所を地図で見る。地理院地図＋Leaflet（無料）を第一候補</t>
         </is>
       </c>
       <c r="F33" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>46327</v>
+        <v>46343</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>絞り込みは実装済</t>
+          <t>CSVの地図列は実装済</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
@@ -2104,26 +2104,30 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>間違い理由タグ</t>
+          <t>漢字・人物などの軸で参照</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
+          <t>テーマ別の一覧ページ（漢字が難しい問題、人物別など）</t>
         </is>
       </c>
       <c r="F34" s="16" t="n">
-        <v>46328</v>
+        <v>46314</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>絞り込みは実装済</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2147,12 +2151,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>復習タイミングの自動化</t>
+          <t>間違い理由タグ</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
+          <t>ド忘れ／漢字ミス／読み飛ばし などを記録し傾向を表示</t>
         </is>
       </c>
       <c r="F35" s="16" t="n">
@@ -2185,17 +2189,17 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>世界の生産量ランキング</t>
+          <t>復習タイミングの自動化</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>FAOSTAT（国連食糧農業機関）のデータで、小麦・米・とうもろこし・大豆などの生産国ランキング問題を作る</t>
+          <t>忘却曲線ベースで「今日復習すべき問題」を出す</t>
         </is>
       </c>
       <c r="F36" s="16" t="n">
@@ -2209,11 +2213,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>一括ダウンロードは登録不要</t>
-        </is>
-      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2237,16 +2237,16 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>世界の生産量ランキング</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>FAOSTAT（国連食糧農業機関）のデータで、小麦・米・とうもろこし・大豆などの生産国ランキング問題を作る</t>
         </is>
       </c>
       <c r="F37" s="16" t="n">
-        <v>46314</v>
+        <v>46328</v>
       </c>
       <c r="G37" s="16" t="n">
         <v>46343</v>
@@ -2256,7 +2256,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>一括ダウンロードは登録不要</t>
+        </is>
+      </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2270,7 +2274,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2280,19 +2284,19 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F38" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2318,17 +2322,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F39" s="16" t="n">
@@ -2366,12 +2370,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F40" s="16" t="n">
@@ -2409,12 +2413,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>人物相関図</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
         </is>
       </c>
       <c r="F41" s="16" t="n">
@@ -2452,12 +2456,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F42" s="16" t="n">
@@ -2490,15 +2494,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+          <t>弱点ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
       <c r="F43" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2524,29 +2532,25 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -2572,17 +2576,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
         </is>
       </c>
       <c r="F45" s="16" t="n">
@@ -2615,21 +2619,21 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
-        <v>46389</v>
+        <v>46374</v>
       </c>
       <c r="G46" s="16" t="n">
         <v>46389</v>
@@ -2658,31 +2662,31 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
       <c r="F47" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="G47" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2696,36 +2700,36 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>46446</v>
+        <v>46419</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2744,35 +2748,31 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>サーバー設計の決定</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>アカウントのモデル・学習記録の持ち方・RLS・課金の表など（シート「サーバー設計」）。Claudeが DDL と RLS の叩き台を作り、決定は本人</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F49" s="16" t="n">
-        <v>46420</v>
+        <v>46433</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>46432</v>
+        <v>46446</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>DBスペシャリストとして判断</t>
-        </is>
-      </c>
+      <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2791,31 +2791,35 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>サーバー設計の決定</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Supabase（PostgreSQL＋認証＋RLS）を第一候補。保護者アカウント＋子どもプロフィール。費用はシート「費用見積」</t>
+          <t>アカウントのモデル・学習記録の持ち方・RLS・課金の表など（シート「サーバー設計」）。Claudeが DDL と RLS の叩き台を作り、決定は本人</t>
         </is>
       </c>
       <c r="F50" s="16" t="n">
-        <v>46433</v>
+        <v>46420</v>
       </c>
       <c r="G50" s="16" t="n">
-        <v>46477</v>
+        <v>46432</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>DBスペシャリストとして判断</t>
+        </is>
+      </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2834,17 +2838,17 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase（PostgreSQL＋認証＋RLS）を第一候補。保護者アカウント＋子どもプロフィール。費用はシート「費用見積」</t>
         </is>
       </c>
       <c r="F51" s="16" t="n">
@@ -2882,12 +2886,12 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F52" s="16" t="n">
@@ -2925,12 +2929,12 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F53" s="16" t="n">
@@ -2963,17 +2967,17 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン移行時のAPI設定</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F54" s="16" t="n">
@@ -2987,11 +2991,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>e-Statはマイページで名称・URLを後から変更できる</t>
-        </is>
-      </c>
+      <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -3010,21 +3010,21 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン移行時のAPI設定</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
         </is>
       </c>
       <c r="F55" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>46477</v>
@@ -3034,7 +3034,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>e-Statはマイページで名称・URLを後から変更できる</t>
+        </is>
+      </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -3048,107 +3052,150 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t>P6 いつか</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>開発</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>白地図に描いて覚える</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>国土数値情報（川・湖・海岸線の形）で白地図を描き、川をなぞる・場所をタップするなどで答える</t>
         </is>
       </c>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="16" t="n"/>
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>自己満足に近いかも。余裕があれば</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J57" s="15" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J58" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E56">
+  <conditionalFormatting sqref="B2:E57">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I56">
+  <conditionalFormatting sqref="B2:I57">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.5"/>
   <cols>
     <col width="4" customWidth="1" style="2" min="1" max="1"/>
@@ -2279,31 +2279,35 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>問題600問へ</t>
+          <t>写真問題の選択肢を意味のあるものに</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>統計問題には出典年を持たせる</t>
+          <t>今は同じ種類（建築・美術・人物）からランダム。寺院どうし・城どうし・同じ時代どうしなど、まぎらわしいものを選ぶようにする（例：平等院鳳凰堂なら中尊寺金色堂・金閣・銀閣）</t>
         </is>
       </c>
       <c r="F38" s="16" t="n">
         <v>46314</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>46343</v>
+        <v>46327</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>ユーザー指摘：鳳凰堂の選択肢に吉野ヶ里遺跡が出るのはおかしい</t>
+        </is>
+      </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2317,7 +2321,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>P3 直前期</t>
+          <t>P2 最難関対策の強化</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2327,19 +2331,19 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>時事問題（2026年）</t>
+          <t>問題600問へ</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
+          <t>統計問題には出典年を持たせる</t>
         </is>
       </c>
       <c r="F39" s="16" t="n">
-        <v>46344</v>
+        <v>46314</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>46373</v>
+        <v>46343</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -2365,17 +2369,17 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>記述問題特訓</t>
+          <t>時事問題（2026年）</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
+          <t>その年の時事は入試頻出。11月〜12月に集中整備</t>
         </is>
       </c>
       <c r="F40" s="16" t="n">
@@ -2413,12 +2417,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>人物相関図</t>
+          <t>記述問題特訓</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
+          <t>模範解答＋採点ポイントのチェックリストで自己採点。専用CSV（記述.csv）</t>
         </is>
       </c>
       <c r="F41" s="16" t="n">
@@ -2456,12 +2460,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>まとめカード</t>
+          <t>人物相関図</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>年表・政治のしくみ図など</t>
+          <t>人物CSV＋関係CSVから図を生成。問題から人物へジャンプ</t>
         </is>
       </c>
       <c r="F42" s="16" t="n">
@@ -2499,12 +2503,12 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>弱点ダッシュボード</t>
+          <t>まとめカード</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>分野・時代・単元ごとの正答率</t>
+          <t>年表・政治のしくみ図など</t>
         </is>
       </c>
       <c r="F43" s="16" t="n">
@@ -2537,15 +2541,19 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>コンテンツ</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>問題1000問へ</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+          <t>弱点ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>分野・時代・単元ごとの正答率</t>
+        </is>
+      </c>
       <c r="F44" s="16" t="n">
         <v>46344</v>
       </c>
@@ -2571,29 +2579,25 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>P4 仕上げ</t>
+          <t>P3 直前期</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>コンテンツ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>総復習モード</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>△×と最近間違えた問題を毎日自動で出題</t>
-        </is>
-      </c>
+          <t>問題1000問へ</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="16" t="n">
-        <v>46374</v>
+        <v>46344</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>46389</v>
+        <v>46373</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -2619,17 +2623,17 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>バグ修正・安定化</t>
+          <t>総復習モード</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>入試直前は新機能より安定を優先</t>
+          <t>△×と最近間違えた問題を毎日自動で出題</t>
         </is>
       </c>
       <c r="F46" s="16" t="n">
@@ -2662,21 +2666,21 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>90日MVP完了</t>
+          <t>バグ修正・安定化</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Day90</t>
+          <t>入試直前は新機能より安定を優先</t>
         </is>
       </c>
       <c r="F47" s="16" t="n">
-        <v>46389</v>
+        <v>46374</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>46389</v>
@@ -2705,31 +2709,31 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>マイルストーン</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>入試本番</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
+          <t>90日MVP完了</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Day90</t>
+        </is>
+      </c>
       <c r="F48" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>46419</v>
+        <v>46389</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>2月以降は機能追加を止める</t>
-        </is>
-      </c>
+      <c r="I48" s="3" t="inlineStr"/>
       <c r="J48" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2743,36 +2747,36 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>P5 一般公開・収益化</t>
+          <t>P4 仕上げ</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>マイルストーン</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare Workersへ移行</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
-        </is>
-      </c>
+          <t>入試本番</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="16" t="n">
-        <v>46433</v>
+        <v>46419</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>46446</v>
+        <v>46419</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>2月以降は機能追加を止める</t>
+        </is>
+      </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2791,35 +2795,31 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>企画</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>サーバー設計の決定</t>
+          <t>Cloudflare Workersへ移行</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>アカウントのモデル・学習記録の持ち方・RLS・課金の表など（シート「サーバー設計」）。Claudeが DDL と RLS の叩き台を作り、決定は本人</t>
+          <t>静的書き出し→@opennextjs/cloudflare。サーバー処理を可能に</t>
         </is>
       </c>
       <c r="F50" s="16" t="n">
-        <v>46420</v>
+        <v>46433</v>
       </c>
       <c r="G50" s="16" t="n">
-        <v>46432</v>
+        <v>46446</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>DBスペシャリストとして判断</t>
-        </is>
-      </c>
+      <c r="I50" s="3" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2838,31 +2838,35 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>企画</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>ログイン・端末間同期</t>
+          <t>サーバー設計の決定</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Supabase（PostgreSQL＋認証＋RLS）を第一候補。保護者アカウント＋子どもプロフィール。費用はシート「費用見積」</t>
+          <t>アカウントのモデル・学習記録の持ち方・RLS・課金の表など（シート「サーバー設計」）。Claudeが DDL と RLS の叩き台を作り、決定は本人</t>
         </is>
       </c>
       <c r="F51" s="16" t="n">
-        <v>46433</v>
+        <v>46420</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>46477</v>
+        <v>46432</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>DBスペシャリストとして判断</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -2881,17 +2885,17 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>開発</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>料金設計・課金</t>
+          <t>ログイン・端末間同期</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>無料枠＋有料（問題数・分析）。Stripe</t>
+          <t>Supabase（PostgreSQL＋認証＋RLS）を第一候補。保護者アカウント＋子どもプロフィール。費用はシート「費用見積」</t>
         </is>
       </c>
       <c r="F52" s="16" t="n">
@@ -2929,12 +2933,12 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>利用規約・プライバシーポリシー</t>
+          <t>料金設計・課金</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>子ども向けサービスのため保護者同意を前提に</t>
+          <t>無料枠＋有料（問題数・分析）。Stripe</t>
         </is>
       </c>
       <c r="F53" s="16" t="n">
@@ -2972,12 +2976,12 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン・集客</t>
+          <t>利用規約・プライバシーポリシー</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>SEO・塾ママ/パパ向けSNS</t>
+          <t>子ども向けサービスのため保護者同意を前提に</t>
         </is>
       </c>
       <c r="F54" s="16" t="n">
@@ -3010,17 +3014,17 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>運用</t>
+          <t>事業</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>独自ドメイン移行時のAPI設定</t>
+          <t>独自ドメイン・集客</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
+          <t>SEO・塾ママ/パパ向けSNS</t>
         </is>
       </c>
       <c r="F55" s="16" t="n">
@@ -3034,11 +3038,7 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>e-Statはマイページで名称・URLを後から変更できる</t>
-        </is>
-      </c>
+      <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -3057,21 +3057,21 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>開発</t>
+          <t>運用</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>保護者ダッシュボード</t>
+          <t>独自ドメイン移行時のAPI設定</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>学習時間・弱点を保護者が確認</t>
+          <t>e-StatのアプリIDは今のCloudflare無料ドメインで登録済み。独自ドメインに移るとき、登録URLの変更（必要なら再発行）と.env.local・Cloudflareの環境変数の更新</t>
         </is>
       </c>
       <c r="F56" s="16" t="n">
-        <v>46447</v>
+        <v>46433</v>
       </c>
       <c r="G56" s="16" t="n">
         <v>46477</v>
@@ -3081,7 +3081,11 @@
           <t>未</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr"/>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>e-Statはマイページで名称・URLを後から変更できる</t>
+        </is>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>e</t>
@@ -3095,107 +3099,150 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
+          <t>P5 一般公開・収益化</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>開発</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>保護者ダッシュボード</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>学習時間・弱点を保護者が確認</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>46447</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>46477</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6">
+        <f>+ROW()-ROW($A$1)</f>
+        <v/>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
           <t>P6 いつか</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>開発</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>白地図に描いて覚える</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>国土数値情報（川・湖・海岸線の形）で白地図を描き、川をなぞる・場所をタップするなどで答える</t>
         </is>
       </c>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="16" t="n"/>
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>自己満足に近いかも。余裕があれば</t>
         </is>
       </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J58" s="15" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J59" s="15" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E57">
+  <conditionalFormatting sqref="B2:E58">
     <cfRule type="expression" priority="1" dxfId="5">
       <formula>B1=B2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:I57">
+  <conditionalFormatting sqref="B2:I58">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H2="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>リスト!$C$3:$C$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -3969,17 +3969,51 @@
         <f>+ROW()-ROW($A$1)</f>
         <v/>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>「4択のみ」の問題の誤答選択肢の見直し</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>選択肢がないと答えられない「どれか」型の203問（出題形式「4択のみ」）に、c0311 のように誤答選択肢がやさしすぎて答えが見えてしまう問題が残っている。主に発展問題（スキャン・筑駒由来）。誤答に正しいとも言えるものがまじっていないかもあわせて確認する</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2：中</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>単元ごとに分けて1問ずつ見直す。誤答は「同じ種類で、まぎらわしいもの」に差しかえる（例：三権分立なら他の向きの権限）。対象は CSV の「出題形式」列が「4択のみ」の行</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>1：未着手</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 に c0311・c0312 は対応済み。答えが語句の74問は「何か」の問い方に直し済み</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="7" t="inlineStr">
         <is>
@@ -5176,7 +5210,7 @@
       <c r="F17" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>青字＝入力値（料金・為替）、黒字＝数式。料金は2026年10月時点の目安</t>
         </is>

--- a/docs/社会学習roadmap.xlsx
+++ b/docs/社会学習roadmap.xlsx
@@ -20,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);-"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -4026,17 +4027,51 @@
         <f>+ROW()-ROW($A$1)</f>
         <v/>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>白地図ドリルの地図が小さい（余白が多い）</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PC・iPad横向きで地図のまわりに余白が多い。原因：(1)地図の大きさは画面の高さで決まる（関東・東北は縦長）(2)白地図ドリル画面のはばの上限が1152px (3)地図を列のまん中に置いている</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>46312</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>自分</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>2：中</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>方向性（未着手）：(1)はばの上限をなくし、地図を左に寄せて画面いっぱいに (2)地図の範囲を、そのセットの地名がおさまる大きさまで自動で切りつめる（縮尺が大きくなる。伊豆大島のように離れた地名があると効きにくい）(3)それでも小さければ、拡大ボタン（＋/−）とずらす操作。ピンの操作とぶつからないように (4)横長の画面では、問題・ボタンを地図の上に重ねて出す案もある。まず(1)(2)から</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>1：未着手</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17 の画面（PC・関東）で、地図の左右に大きな余白</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="n"/>
       <c r="N14" s="7" t="inlineStr">
         <is>
